--- a/Job_Pipeline_Agent_TestCases.xlsx
+++ b/Job_Pipeline_Agent_TestCases.xlsx
@@ -593,12 +593,12 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Test builds profile from a text PDF with a stubbed LLM: experience (2 jobs), projects, skills, education parsed; dates normalised (Jan 2022 -&gt; 2022-01, Present -&gt; present); bullets get ids e1b1/p1b1; profile.json round-trips through schema.</t>
+          <t>1 automated test(s) passed: valid_resume_builds_profile_with_dates</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Automated: tests/unit/test_prf01_profile_builder.py::test_tc001. LLM was stubbed - real-model extraction accuracy NOT verified (no API key).</t>
+          <t>LLM stubbed: checks our PDF/validation/date/safety code, not a real model's accuracy.</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Corrupt PDF -&gt; ProfileBuildError 'could not read PDF'; image-only (scanned) PDF -&gt; error 'looks like a scanned/image-only PDF'; missing file and 'nothing extracted' also error. In all cases profile.json is not created and the LLM is not called for bad PDFs.</t>
+          <t>4 automated test(s) passed: corrupt_pdf_gives_clear_error_and_saves_nothing; scanned_image_only_pdf_gives_clear_error_and_saves_nothing; missing_file; ...</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Automated: test_tc002_* (4 tests). Scan detection is 'no text layer'; a scanned PDF with an OCR text layer would be treated as readable.</t>
+          <t>LLM stubbed: checks our PDF/validation/date/safety code, not a real model's accuracy.</t>
         </is>
       </c>
     </row>
@@ -697,12 +697,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Resume without projects -&gt; profile.json saved with projects=[] and warning 'No projects section found in the resume'.</t>
+          <t>1 automated test(s) passed: no_projects_section_builds_profile_with_warning</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Automated: test_tc003. Warning is based on the extractor returning no projects (stubbed).</t>
+          <t>LLM stubbed: checks our PDF/validation/date/safety code, not a real model's accuracy.</t>
         </is>
       </c>
     </row>
@@ -744,11 +744,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: ctc_in_resume_never_reaches_sensitive_fields</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Verified in the PRF-01 test file; sensitive section is structurally unreachable for the LLM.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -788,11 +796,15 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: null_notice_period_warns_at_startup; null_notice_period_fails_fast_in_strict_mode</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -832,11 +844,15 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: discovery_uses_the_users_search_preferences</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -876,11 +892,15 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: min_experience_above_max_is_a_validation_error</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -920,11 +940,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: edited_profile_gets_new_hash_and_old_applications_keep_old_hash</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -964,11 +988,15 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: saving_unchanged_profile_keeps_same_hash</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1008,11 +1036,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: five_linkedin_alert_emails_parse_all_jobs</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1052,11 +1088,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: five_naukri_alert_emails_parse_all_jobs</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1096,11 +1140,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_email_processed_twice_inserts_no_duplicates</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1140,11 +1192,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: changed_template_logs_error_alerts_and_does_not_crash</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1184,11 +1244,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: job_posted_2_days_ago_is_kept</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1228,11 +1296,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: job_posted_4_days_ago_is_dropped</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1272,11 +1348,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: job_posted_exactly_3_days_ago_is_kept_boundary</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1316,11 +1400,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: missing_posted_date_is_kept_and_flagged_consistently</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1360,11 +1452,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_job_from_linkedin_and_naukri_gives_one_row</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1404,11 +1504,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_job_with_different_tracking_params_is_one_row</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1448,11 +1556,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_company_different_titles_give_two_rows</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1492,11 +1608,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: sales_and_bpo_titles_are_rejected</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1536,11 +1660,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: genai_engineer_passes</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1580,11 +1712,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: blacklist_and_whitelist_both_match_has_deterministic_documented_outcome</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1624,11 +1764,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: empty_gmail_result_raises_zero_jobs_alert</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1668,11 +1816,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: expired_gmail_token_raises_auth_failed_alert_not_silent</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic .eml fixtures (tests/fixtures/emails), not real captured alerts; Gmail is a fake MailSource. Auth failure simulated by a MailSource that raises MailAuthError.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1712,11 +1868,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: clear_jd_extracts_skills_experience_and_location; rule_extractor_matches_on_the_same_jd</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Rule-based extractor also tested. No real model measured.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1756,11 +1920,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: jd_without_salary_keeps_salary_null_even_if_llm_hallucinates; real_salary_in_jd_is_kept</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Rule-based extractor also tested. No real model measured.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1800,11 +1972,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: invalid_json_retries_once_then_extraction_failed; second_attempt_can_succeed</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Rule-based extractor also tested. No real model measured.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1844,11 +2024,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: login_wall_falls_back_to_snippet_with_jd_partial_and_continues; http_403_also_gives_jd_partial</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Rule-based extractor also tested. No real model measured.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1888,11 +2076,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: perfect_match_jd_scores_80_or_more; score_has_a_reason_of_at_most_two_lines</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TC-030/031/033 use the deterministic rule scorer; TC-032/034 use a stubbed LLM. A live model's score consistency was not measured.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1932,11 +2128,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: irrelevant_sap_jd_scores_below_50</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TC-030/031/033 use the deterministic rule scorer; TC-032/034 use a stubbed LLM. A live model's score consistency was not measured.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1976,11 +2180,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: wrong_llm_total_is_recomputed_from_components; out_of_range_component_is_rejected_and_retried</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TC-030/031/033 use the deterministic rule scorer; TC-032/034 use a stubbed LLM. A live model's score consistency was not measured.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2020,11 +2232,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_jd_scored_twice_differs_by_less_than_5</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TC-030/031/033 use the deterministic rule scorer; TC-032/034 use a stubbed LLM. A live model's score consistency was not measured. Deterministic scorer returns identical scores (diff 0).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2064,11 +2284,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: ai_labelled_support_job_gets_low_role_type_even_if_llm_says_high</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TC-030/031/033 use the deterministic rule scorer; TC-032/034 use a stubbed LLM. A live model's score consistency was not measured.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2108,11 +2336,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: scores_70_and_69_land_in_apply_and_maybe</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed to emit exact component totals.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2152,11 +2388,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: scores_50_and_49_land_in_maybe_and_reject</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed to emit exact component totals.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2196,11 +2440,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: digest_with_10_scored_jobs_lists_apply_first_with_score_and_reason</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Digest channel is an in-memory fake (no real email/Telegram).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2240,11 +2492,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: no_new_scored_jobs_sends_no_new_matches_not_an_empty_digest</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Digest channel is an in-memory fake (no real email/Telegram).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2284,11 +2544,15 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: manual_apply_moves_a_rejected_job_forward</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2328,11 +2592,15 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: skipping_an_apply_job_sets_skipped_and_it_does_not_come_back</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2372,11 +2640,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: langchain_heavy_jd_puts_langchain_bullets_first; ordering_is_enforced_even_if_the_llm_returns_a_different_order</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2416,11 +2692,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: every_output_bullet_traces_back_to_an_original_id</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2460,11 +2744,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: kubernetes_in_jd_but_not_in_profile_never_reaches_the_resume</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2504,11 +2796,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: rewrite_with_a_number_not_in_the_original_is_rejected</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2548,11 +2848,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: changing_company_role_or_dates_is_rejected</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2592,11 +2900,19 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: validator_catches_all_10_deliberately_bad_drafts</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2636,11 +2952,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: validator_failing_twice_uses_base_resume_and_flags_it</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2680,11 +3004,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: diff_highlights_changed_lines_and_not_unchanged_ones; identical_resumes_have_an_empty_diff</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2724,11 +3056,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: pdf_text_has_correct_reading_order_and_all_sections</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2768,11 +3108,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: pdf_is_single_column_without_tables_or_images</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2812,11 +3160,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: content_heavy_profile_still_renders_in_at_most_2_pages</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LLM stubbed. Ordering is done in code. PDF made with reportlab (LLD said Playwright).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2856,11 +3212,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: greenhouse_style_form_gets_name_email_phone_links_filled</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2900,11 +3264,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: three_page_form_is_crossed_and_agent_stops_at_submit</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2944,11 +3316,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: email_comes_from_the_profile_with_zero_llm_calls</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2988,11 +3368,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>3 automated test(s) passed: different_phone_labels_all_map_to_the_same_profile_key; different_phone_labels_all_map_to_the_same_profile_key; different_phone_labels_all_map_to_the_same_profile_key</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3032,11 +3420,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: same_question_in_another_form_is_answered_from_the_bank_without_llm</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3076,11 +3472,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: slightly_rephrased_question_above_0_90_reuses_the_bank_answer</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched. Similarity is char-trigram cosine (offline), not a semantic embedding model.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3120,11 +3524,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: question_below_0_90_similarity_gets_a_new_draft</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched. Similarity is char-trigram cosine (offline), not a semantic embedding model.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3164,11 +3576,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: custom_question_draft_is_at_most_80_words_and_flagged_for_review</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3208,11 +3628,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: dropdown_answer_is_always_one_of_the_options; an_answer_outside_the_options_is_never_filled</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3252,11 +3680,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: every_field_gets_a_row_with_question_answer_source_confidence</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3296,11 +3732,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: recaptcha_page_goes_to_needs_human_with_no_bypass_attempt; recaptcha_page_goes_to_needs_human_with_no_bypass_attempt</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3340,11 +3784,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: unknown_widget_custom_datepicker_needs_human_without_crashing</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3384,11 +3836,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: sensitive_field_missing_in_profile_is_not_guessed_and_needs_human</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3428,11 +3888,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: clicking_a_submit_button_in_the_fill_phase_raises_submit_blocked; even_a_programmatic_submit_is_cancelled_during_fill</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3472,11 +3940,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>6 automated test(s) passed: submit_like_button_texts_are_all_blocked; submit_like_button_texts_are_all_blocked; submit_like_button_texts_are_all_blocked; ...</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; LLM stubbed; no real ATS/site was touched.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3516,11 +3992,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: review_screen_shows_screenshot_field_table_and_resume_diff</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3560,11 +4044,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: needs_review_rows_are_highlighted_and_editable_others_are_not</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3604,11 +4096,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr"/>
-      <c r="J70" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: approve_runs_the_submit_flow</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3648,11 +4148,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: skip_sets_skipped_and_nothing_is_submitted</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3692,11 +4200,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: edited_answer_is_what_gets_submitted_not_the_original</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3736,11 +4252,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: edited_answer_is_saved_to_the_bank_with_human_approved</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3780,11 +4304,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: next_form_with_a_similar_question_gets_the_edited_answer</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3824,11 +4356,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: sixteenth_application_is_blocked_with_a_limit_reached_message; cap_is_configurable</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3868,11 +4408,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: two_consecutive_submits_are_45_to_120_seconds_apart</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3912,11 +4460,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: successful_submit_saves_confirmation_screenshot_and_timestamp</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3956,11 +4512,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: no_confirmation_page_gives_submit_uncertain_and_no_retry</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4000,11 +4564,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: second_submit_on_the_same_job_is_blocked</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4044,11 +4616,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: submit_uncertain_job_is_never_auto_submitted</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4088,11 +4668,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: page_structure_changed_since_review_aborts_to_needs_human_without_submitting; new_required_field_appearing_also_aborts</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Real headless Chromium on local dummy forms; no real employer site. Time/delay uses a fake clock.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4132,11 +4720,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: three_company_emails_within_48_hours_are_all_fetched_and_processed</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4176,11 +4772,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr"/>
-      <c r="J83" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: newsletters_and_unrelated_emails_are_ignored</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4220,11 +4824,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: application_received_email_sets_received</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4264,11 +4876,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: interview_email_sets_interview_scheduled_and_extracts_datetime</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4308,11 +4928,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr"/>
-      <c r="J86" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: rejection_email_sets_rejected</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4352,11 +4980,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: ambiguous_email_is_labelled_other_and_status_is_not_updated</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4396,11 +5032,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: interview_email_raises_immediate_alert_with_calendar_suggestion</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4440,11 +5084,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: interview_email_without_datetime_alerts_but_creates_no_blank_event</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4484,11 +5136,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr"/>
-      <c r="J90" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: no_reply_for_14_days_marks_ghosted</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4528,11 +5188,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: 13_days_without_reply_changes_nothing</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4572,11 +5240,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr"/>
-      <c r="J92" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: reply_on_day_10_prevents_ghosting_at_day_14</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4616,11 +5292,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: two_roles_at_one_company_and_an_unclear_email_goes_to_manual_list; the_same_company_email_that_names_the_role_is_matched</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4660,11 +5344,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: low_score_or_small_margin_goes_to_manual_list</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Gmail is a fake MailSource; classifier is rule-based (LLM fallback not exercised).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4704,11 +5396,15 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: funnel_report_shows_exactly_the_known_numbers</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4748,11 +5444,15 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: empty_week_gives_a_report_of_zeros_without_crashing</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4792,11 +5492,15 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: bucket_80_plus_with_5_applied_2_positive_shows_40_percent</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4836,11 +5540,15 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr"/>
-      <c r="J98" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: bucket_with_zero_applications_has_no_division_error</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4880,11 +5588,15 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: two_conflicting_answers_to_the_same_question_are_flagged; duplicates_with_the_same_answer_are_merged</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4924,11 +5636,15 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: human_approved_answer_is_never_overwritten_by_cleanup; merging_duplicates_keeps_the_human_approved_flag</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4968,11 +5684,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: mapper_accuracy_on_20_golden_forms_meets_the_90_percent_target</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>20 hand-written golden forms (189 fields), not captured from real sites. First run 96.8%; rules were then fixed to 100% on this same set.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5012,11 +5736,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: a_change_that_lowers_accuracy_is_flagged_as_a_regression</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>20 hand-written golden forms (189 fields), not captured from real sites. First run 96.8%; rules were then fixed to 100% on this same set.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5056,11 +5788,15 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: fresh_install_has_auto_submit_false; only_an_explicit_config_value_turns_it_on</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5100,11 +5836,15 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr"/>
-      <c r="J104" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: auto_submit_off_by_default_blocks_unreviewed_submit_and_on_allows_it</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5144,11 +5884,15 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: no_sensitive_value_appears_in_any_logged_llm_prompt</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5188,11 +5932,15 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr"/>
-      <c r="J106" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: notice_period_and_expected_ctc_come_only_from_profile_json</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5232,11 +5980,15 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr"/>
-      <c r="J107" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: every_tailored_resume_for_many_jds_only_contains_profile_claims</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5276,11 +6028,15 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr"/>
-      <c r="J108" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: a_job_failing_three_times_becomes_failed_and_others_keep_going; a_failing_job_does_not_block_the_batch_within_one_run</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5320,11 +6076,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr"/>
-      <c r="J109" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: job_locked_by_a_crashed_worker_is_picked_up_again_after_the_lease</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>Crash simulated by claiming a job and never finishing it.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5364,11 +6128,15 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>2 automated test(s) passed: every_llm_call_logs_tokens_cost_and_latency; failed_calls_are_logged_too</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5408,11 +6176,15 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: full_status_history_of_a_job_is_traceable_end_to_end</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5452,11 +6224,15 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: logs_never_contain_passwords_tokens_or_ctc_in_plain_text</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5496,11 +6272,15 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr"/>
-      <c r="J113" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: running_any_step_twice_creates_no_duplicate_data</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5540,11 +6320,15 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>1 automated test(s) passed: dry_run_executes_the_flow_but_writes_nothing_and_logs_instead</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5584,11 +6368,15 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr"/>
-      <c r="J115" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>4 automated test(s) passed: llm_429_is_retried_with_exponential_backoff; persistent_429_gives_up_after_3_retries_with_doubling_delays; a_job_whose_llm_keeps_429ing_gets_attempts_incremented_not_lost; ...</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5628,11 +6416,15 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr"/>
-      <c r="J116" s="3" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>3 automated test(s) passed: discovered_straight_to_submitted_raises_and_leaves_status_unchanged; every_pair_of_statuses_behaves_exactly_as_the_table_says; unknown_status_is_rejected</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J116"/>
